--- a/data/trans_dic/DC-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DC-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,72; 19,2</t>
+          <t>13,0; 19,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,72</t>
+          <t>5,45; 10,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 14,05</t>
+          <t>8,04; 14,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,76; 21,8</t>
+          <t>14,9; 21,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,78; 26,19</t>
+          <t>16,82; 26,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,82; 24,1</t>
+          <t>15,3; 24,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,35</t>
+          <t>8,73; 16,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,62; 38,43</t>
+          <t>30,54; 38,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,29; 20,8</t>
+          <t>15,24; 20,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,16</t>
+          <t>10,26; 15,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 13,87</t>
+          <t>9,17; 13,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,02; 28,4</t>
+          <t>23,0; 28,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,3; 15,48</t>
+          <t>8,49; 15,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 12,81</t>
+          <t>6,62; 12,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,13</t>
+          <t>3,66; 9,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 23,36</t>
+          <t>16,09; 23,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,26; 34,46</t>
+          <t>24,89; 34,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,21; 24,2</t>
+          <t>15,0; 23,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 21,87</t>
+          <t>13,72; 21,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,1; 39,81</t>
+          <t>31,78; 39,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 23,81</t>
+          <t>17,54; 23,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 16,54</t>
+          <t>11,28; 16,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 14,0</t>
+          <t>9,26; 14,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 29,72</t>
+          <t>23,85; 29,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 23,86</t>
+          <t>17,14; 24,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,56</t>
+          <t>9,14; 14,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 11,64</t>
+          <t>6,61; 11,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 26,28</t>
+          <t>6,38; 26,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,0; 37,58</t>
+          <t>23,68; 38,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 28,14</t>
+          <t>17,71; 28,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,4; 31,78</t>
+          <t>18,83; 32,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,97; 50,95</t>
+          <t>38,98; 50,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,48; 26,16</t>
+          <t>19,56; 25,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,56; 17,7</t>
+          <t>12,67; 17,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,45</t>
+          <t>10,31; 15,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 31,55</t>
+          <t>10,07; 31,15</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 24,19</t>
+          <t>19,29; 24,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 14,96</t>
+          <t>11,05; 15,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,51</t>
+          <t>8,73; 12,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,63; 26,99</t>
+          <t>21,77; 27,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,73; 33,42</t>
+          <t>26,73; 33,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 25,0</t>
+          <t>18,98; 24,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 20,06</t>
+          <t>14,52; 20,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,05; 74,0</t>
+          <t>35,0; 69,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,83; 26,9</t>
+          <t>22,78; 26,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 18,36</t>
+          <t>14,83; 18,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 14,93</t>
+          <t>11,63; 14,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,71; 54,08</t>
+          <t>28,66; 57,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 25,06</t>
+          <t>16,32; 25,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 12,39</t>
+          <t>7,23; 12,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,68; 15,99</t>
+          <t>10,86; 16,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,37; 29,31</t>
+          <t>21,5; 29,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,18; 31,98</t>
+          <t>23,85; 31,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,34; 31,14</t>
+          <t>24,83; 31,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,02; 26,19</t>
+          <t>19,69; 26,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,99; 62,62</t>
+          <t>43,07; 62,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,12; 27,99</t>
+          <t>22,18; 27,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,93</t>
+          <t>18,39; 22,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 20,94</t>
+          <t>16,53; 20,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,93; 50,78</t>
+          <t>35,92; 50,33</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,48</t>
+          <t>0,97; 4,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,09</t>
+          <t>1,49; 6,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,02</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 19,12</t>
+          <t>5,55; 19,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,26; 30,26</t>
+          <t>25,06; 29,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,96; 28,22</t>
+          <t>22,87; 28,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,09</t>
+          <t>15,27; 19,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,32; 39,67</t>
+          <t>33,41; 39,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,62; 24,66</t>
+          <t>20,64; 24,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,98; 23,58</t>
+          <t>18,69; 23,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,17; 16,28</t>
+          <t>12,2; 16,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,42; 33,19</t>
+          <t>27,3; 33,44</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,21; 18,94</t>
+          <t>16,34; 18,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,48</t>
+          <t>9,32; 11,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,56</t>
+          <t>8,54; 10,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 22,2</t>
+          <t>15,88; 22,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,37; 29,55</t>
+          <t>26,4; 29,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,31; 25,36</t>
+          <t>22,34; 25,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 19,71</t>
+          <t>17,01; 19,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,72; 55,36</t>
+          <t>38,38; 52,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,82; 23,85</t>
+          <t>21,71; 23,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,26; 18,12</t>
+          <t>16,35; 18,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,17; 14,94</t>
+          <t>13,05; 14,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,51; 39,46</t>
+          <t>28,62; 38,57</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60261; 90956</t>
+          <t>61578; 93852</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24325; 46880</t>
+          <t>23815; 46692</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32653; 60277</t>
+          <t>34518; 60969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74562; 110142</t>
+          <t>75295; 108461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51469; 80331</t>
+          <t>51587; 80514</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46590; 75780</t>
+          <t>48119; 76760</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30793; 56733</t>
+          <t>30281; 56103</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>136992; 171972</t>
+          <t>136668; 170052</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>119293; 162346</t>
+          <t>118948; 162888</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77242; 113943</t>
+          <t>77133; 116535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70227; 107624</t>
+          <t>71179; 107149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>219282; 270529</t>
+          <t>219073; 270264</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30452; 56789</t>
+          <t>31147; 55602</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27654; 53636</t>
+          <t>27735; 52926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14029; 34440</t>
+          <t>13788; 34326</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71681; 105642</t>
+          <t>72740; 104285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93929; 128139</t>
+          <t>92570; 126792</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51419; 81783</t>
+          <t>50712; 80009</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50372; 81409</t>
+          <t>51079; 78847</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>119000; 152292</t>
+          <t>121574; 152302</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131710; 175932</t>
+          <t>129592; 174723</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85477; 125160</t>
+          <t>85398; 124774</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69855; 104929</t>
+          <t>69402; 105139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>198961; 248093</t>
+          <t>199072; 247617</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91824; 129425</t>
+          <t>92958; 130334</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57571; 91657</t>
+          <t>57534; 91173</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34493; 60755</t>
+          <t>34493; 61505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36246; 175630</t>
+          <t>42623; 175203</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40274; 63053</t>
+          <t>39729; 63917</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46590; 73203</t>
+          <t>46076; 72910</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30560; 52789</t>
+          <t>31273; 53493</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65042; 85047</t>
+          <t>65065; 84373</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>138345; 185764</t>
+          <t>138933; 184369</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111694; 157465</t>
+          <t>112694; 156987</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71679; 106327</t>
+          <t>70953; 107146</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77994; 263516</t>
+          <t>84091; 260154</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238466; 299506</t>
+          <t>238841; 300914</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128925; 173394</t>
+          <t>128101; 174871</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98448; 143777</t>
+          <t>100371; 140336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>223796; 279249</t>
+          <t>225304; 282037</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>190956; 238746</t>
+          <t>190898; 240254</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>144617; 191639</t>
+          <t>145520; 191380</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120242; 165650</t>
+          <t>119950; 166219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>342823; 723744</t>
+          <t>342335; 683907</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>445729; 525231</t>
+          <t>444895; 519844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>284501; 353485</t>
+          <t>285536; 352208</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>233608; 295025</t>
+          <t>229687; 293642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>577888; 1088639</t>
+          <t>576930; 1154205</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57282; 87862</t>
+          <t>57198; 87665</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36974; 63281</t>
+          <t>36899; 65100</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66263; 99237</t>
+          <t>67396; 102106</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101526; 139229</t>
+          <t>102157; 140666</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>137513; 181861</t>
+          <t>135652; 178449</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185376; 237108</t>
+          <t>189109; 241209</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>147763; 193312</t>
+          <t>145339; 192694</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>361689; 526805</t>
+          <t>362370; 526461</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203344; 257272</t>
+          <t>203891; 256639</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>230036; 291635</t>
+          <t>233991; 288321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>225569; 284603</t>
+          <t>224579; 282438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>473011; 668517</t>
+          <t>472830; 662499</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2901; 13354</t>
+          <t>2895; 13717</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3983; 16256</t>
+          <t>3969; 17772</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>963; 8665</t>
+          <t>0; 8357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14339; 45985</t>
+          <t>13337; 45843</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>315473; 377841</t>
+          <t>312903; 374408</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>254721; 313109</t>
+          <t>253660; 311641</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>165098; 217387</t>
+          <t>165172; 216227</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>253652; 302059</t>
+          <t>254408; 300214</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>318962; 381545</t>
+          <t>319296; 385366</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>261276; 324523</t>
+          <t>257159; 320816</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166571; 222857</t>
+          <t>166978; 222649</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>274754; 332495</t>
+          <t>273471; 335039</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>530255; 619456</t>
+          <t>534369; 620513</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>316414; 392970</t>
+          <t>318916; 393120</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>290451; 357440</t>
+          <t>289043; 359668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>536315; 749654</t>
+          <t>536201; 749068</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>890873; 998230</t>
+          <t>891815; 991245</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>792204; 900252</t>
+          <t>793031; 896331</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>601868; 696035</t>
+          <t>600575; 698324</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1385146; 1980594</t>
+          <t>1373081; 1886540</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1450634; 1585790</t>
+          <t>1443649; 1581040</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1133862; 1263203</t>
+          <t>1140015; 1263448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>911118; 1033257</t>
+          <t>902913; 1026419</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1982642; 2743669</t>
+          <t>1990378; 2682017</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DC-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 19,81</t>
+          <t>12,93; 19,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,68</t>
+          <t>5,53; 10,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 14,21</t>
+          <t>7,77; 13,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,9; 21,47</t>
+          <t>14,98; 21,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,82; 26,25</t>
+          <t>16,88; 26,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,3; 24,41</t>
+          <t>15,16; 25,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 16,17</t>
+          <t>8,85; 15,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,54; 38,0</t>
+          <t>31,05; 38,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 20,87</t>
+          <t>15,5; 21,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 15,5</t>
+          <t>10,27; 15,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 13,81</t>
+          <t>9,18; 13,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 28,37</t>
+          <t>23,6; 28,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 15,15</t>
+          <t>8,36; 14,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,64</t>
+          <t>6,59; 12,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,1</t>
+          <t>3,83; 8,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,09; 23,06</t>
+          <t>15,78; 22,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,89; 34,1</t>
+          <t>24,78; 34,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,0; 23,67</t>
+          <t>14,8; 23,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 21,18</t>
+          <t>13,4; 21,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,78; 39,81</t>
+          <t>32,57; 40,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,54; 23,65</t>
+          <t>17,81; 23,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,28; 16,49</t>
+          <t>11,23; 16,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,03</t>
+          <t>9,24; 14,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,85; 29,66</t>
+          <t>24,54; 30,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,14; 24,03</t>
+          <t>16,94; 23,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 14,49</t>
+          <t>9,23; 14,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 11,78</t>
+          <t>6,65; 11,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 26,22</t>
+          <t>20,82; 28,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,68; 38,1</t>
+          <t>23,08; 38,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 28,03</t>
+          <t>17,18; 28,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,83; 32,2</t>
+          <t>18,27; 31,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,98; 50,55</t>
+          <t>39,71; 51,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,56; 25,96</t>
+          <t>19,9; 26,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,65</t>
+          <t>12,35; 17,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 15,57</t>
+          <t>10,19; 15,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 31,15</t>
+          <t>27,17; 34,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 24,3</t>
+          <t>19,46; 24,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,05; 15,09</t>
+          <t>11,14; 15,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,21</t>
+          <t>8,78; 12,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,77; 27,25</t>
+          <t>21,33; 26,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,73; 33,64</t>
+          <t>26,79; 33,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 24,96</t>
+          <t>18,88; 25,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 20,13</t>
+          <t>14,5; 19,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,0; 69,92</t>
+          <t>33,95; 39,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,78; 26,62</t>
+          <t>22,78; 26,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,83; 18,29</t>
+          <t>14,73; 18,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,63; 14,86</t>
+          <t>11,83; 15,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,66; 57,34</t>
+          <t>27,39; 31,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 25,01</t>
+          <t>16,22; 24,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,75</t>
+          <t>7,13; 12,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,86; 16,45</t>
+          <t>10,74; 16,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,5; 29,61</t>
+          <t>20,45; 28,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,85; 31,38</t>
+          <t>24,0; 31,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,83; 31,67</t>
+          <t>24,38; 31,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,69; 26,1</t>
+          <t>19,74; 26,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 62,57</t>
+          <t>43,07; 48,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,18; 27,92</t>
+          <t>22,11; 27,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 22,66</t>
+          <t>18,18; 22,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,53; 20,78</t>
+          <t>16,59; 20,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,92; 50,33</t>
+          <t>34,69; 39,49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,6</t>
+          <t>1,0; 4,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,66</t>
+          <t>1,4; 6,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,34; 3,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 19,06</t>
+          <t>6,34; 18,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,87; 28,09</t>
+          <t>23,04; 28,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,27; 19,98</t>
+          <t>15,21; 19,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,41; 39,43</t>
+          <t>33,27; 39,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,64; 24,91</t>
+          <t>20,61; 24,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,69; 23,31</t>
+          <t>18,92; 23,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,26</t>
+          <t>12,18; 16,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,3; 33,44</t>
+          <t>27,53; 33,4</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,97</t>
+          <t>16,13; 18,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,32; 11,49</t>
+          <t>9,33; 11,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 10,62</t>
+          <t>8,56; 10,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,88; 22,19</t>
+          <t>20,04; 23,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,4; 29,34</t>
+          <t>26,46; 29,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,34; 25,25</t>
+          <t>22,37; 25,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,01; 19,77</t>
+          <t>17,01; 19,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,38; 52,73</t>
+          <t>37,34; 40,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,71; 23,78</t>
+          <t>21,81; 23,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 18,12</t>
+          <t>16,31; 18,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,05; 14,84</t>
+          <t>13,17; 14,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,62; 38,57</t>
+          <t>29,27; 31,3</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>153706</t>
+          <t>169222</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>244405</t>
+          <t>268909</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61578; 93852</t>
+          <t>61279; 92236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23815; 46692</t>
+          <t>24198; 46863</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34518; 60969</t>
+          <t>33354; 60038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75295; 108461</t>
+          <t>82489; 118618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51587; 80514</t>
+          <t>51759; 79874</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48119; 76760</t>
+          <t>47661; 78611</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30281; 56103</t>
+          <t>30727; 55492</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>136668; 170052</t>
+          <t>151668; 188909</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118948; 162888</t>
+          <t>121000; 165528</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77133; 116535</t>
+          <t>77194; 113865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71179; 107149</t>
+          <t>71254; 106911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>219073; 270264</t>
+          <t>245201; 296396</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87724</t>
+          <t>92354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>135659</t>
+          <t>154226</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>223383</t>
+          <t>246581</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31147; 55602</t>
+          <t>30687; 54553</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27735; 52926</t>
+          <t>27619; 53690</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13788; 34326</t>
+          <t>14449; 33611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72740; 104285</t>
+          <t>76272; 109802</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92570; 126792</t>
+          <t>92160; 126618</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50712; 80009</t>
+          <t>50021; 80645</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51079; 78847</t>
+          <t>49876; 79606</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>121574; 152302</t>
+          <t>137804; 172919</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>129592; 174723</t>
+          <t>131602; 173706</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85398; 124774</t>
+          <t>85005; 126114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69402; 105139</t>
+          <t>69274; 105158</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>199072; 247617</t>
+          <t>222427; 275521</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105808</t>
+          <t>116541</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74891</t>
+          <t>84731</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>180698</t>
+          <t>201273</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92958; 130334</t>
+          <t>91901; 129625</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57534; 91173</t>
+          <t>58077; 90767</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34493; 61505</t>
+          <t>34723; 61106</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42623; 175203</t>
+          <t>98179; 135669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39729; 63917</t>
+          <t>38719; 63812</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46076; 72910</t>
+          <t>44680; 73367</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31273; 53493</t>
+          <t>30350; 52802</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65065; 84373</t>
+          <t>74461; 95877</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>138933; 184369</t>
+          <t>141342; 185602</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112694; 156987</t>
+          <t>109833; 154936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70953; 107146</t>
+          <t>70086; 107275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84091; 260154</t>
+          <t>179047; 224593</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250248</t>
+          <t>267283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>484564</t>
+          <t>316060</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>734812</t>
+          <t>583344</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238841; 300914</t>
+          <t>240989; 298855</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128101; 174871</t>
+          <t>129108; 176667</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100371; 140336</t>
+          <t>100991; 142836</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>225304; 282037</t>
+          <t>241476; 300195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>190898; 240254</t>
+          <t>191338; 237446</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>145520; 191380</t>
+          <t>144763; 194963</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119950; 166219</t>
+          <t>119711; 164262</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>342335; 683907</t>
+          <t>292421; 340678</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>444895; 519844</t>
+          <t>444748; 520308</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>285536; 352208</t>
+          <t>283673; 354321</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229687; 293642</t>
+          <t>233773; 297990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>576930; 1154205</t>
+          <t>545877; 620532</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119551</t>
+          <t>135801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>414083</t>
+          <t>380670</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>533634</t>
+          <t>516471</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57198; 87665</t>
+          <t>56877; 85484</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36899; 65100</t>
+          <t>36390; 63937</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67396; 102106</t>
+          <t>66688; 101176</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102157; 140666</t>
+          <t>116171; 160021</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>135652; 178449</t>
+          <t>136482; 180467</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>189109; 241209</t>
+          <t>185636; 236039</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>145339; 192694</t>
+          <t>145738; 194173</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>362370; 526461</t>
+          <t>357853; 404924</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203891; 256639</t>
+          <t>203237; 256155</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>233991; 288321</t>
+          <t>231316; 289135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>224579; 282438</t>
+          <t>225513; 285027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>472830; 662499</t>
+          <t>485254; 552407</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25989</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>277804</t>
+          <t>304284</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>303793</t>
+          <t>329977</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2895; 13717</t>
+          <t>2994; 13547</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3969; 17772</t>
+          <t>3736; 17695</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 8357</t>
+          <t>971; 8746</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13337; 45843</t>
+          <t>15034; 43298</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>312903; 374408</t>
+          <t>312963; 374397</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>253660; 311641</t>
+          <t>255549; 316730</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>165172; 216227</t>
+          <t>164610; 215067</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>254408; 300214</t>
+          <t>280861; 332056</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>319296; 385366</t>
+          <t>318837; 381463</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257159; 320816</t>
+          <t>260368; 321941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166978; 222649</t>
+          <t>166739; 220028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>273471; 335039</t>
+          <t>297752; 361242</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>680020</t>
+          <t>737360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1540706</t>
+          <t>1409194</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2220726</t>
+          <t>2146554</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>534369; 620513</t>
+          <t>527510; 619339</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>318916; 393120</t>
+          <t>319354; 390932</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>289043; 359668</t>
+          <t>289884; 360242</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>536201; 749068</t>
+          <t>690030; 793642</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>891815; 991245</t>
+          <t>893927; 997024</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>793031; 896331</t>
+          <t>794293; 898286</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>600575; 698324</t>
+          <t>600584; 697584</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1373081; 1886540</t>
+          <t>1357371; 1457286</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1443649; 1581040</t>
+          <t>1450171; 1581970</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1140015; 1263448</t>
+          <t>1137017; 1264100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>902913; 1026419</t>
+          <t>911177; 1028242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1990378; 2682017</t>
+          <t>2071994; 2215240</t>
         </is>
       </c>
     </row>
